--- a/app/reports/CYBN_research.xlsx
+++ b/app/reports/CYBN_research.xlsx
@@ -616,7 +616,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04947000026702881</v>
+        <v>0.04974999904632568</v>
       </c>
     </row>
     <row r="6">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>237270960</v>
+        <v>238945824</v>
       </c>
       <c r="D6" s="30" t="n"/>
       <c r="E6" s="30" t="n">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>133024216</v>
+        <v>137441984</v>
       </c>
       <c r="D7" s="30" t="n"/>
       <c r="E7" s="30" t="n">
-        <v>-3.332</v>
+        <v>-3.541</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>68.929</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>211672144</v>
+        <v>208879648</v>
       </c>
       <c r="D8" s="30" t="n"/>
       <c r="E8" s="30" t="n">
-        <v>-3.087</v>
+        <v>-3.07</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>18.277</v>
+        <v>18.173</v>
       </c>
     </row>
     <row r="9">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>123514448</v>
+        <v>122020472</v>
       </c>
       <c r="D9" s="30" t="n"/>
       <c r="E9" s="30" t="n">
-        <v>-1.524</v>
+        <v>-1.398</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>50.866</v>
+        <v>46.662</v>
       </c>
     </row>
     <row r="10">
@@ -1606,11 +1606,11 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>207711904</v>
+        <v>208428144</v>
       </c>
       <c r="D11" s="30" t="n"/>
       <c r="E11" s="30" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.874</v>
       </c>
       <c r="F11" s="30" t="n"/>
     </row>
@@ -1626,11 +1626,11 @@
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>205778416</v>
+        <v>206124272</v>
       </c>
       <c r="D12" s="30" t="n"/>
       <c r="E12" s="30" t="n">
-        <v>-1.44</v>
+        <v>-1.403</v>
       </c>
       <c r="F12" s="30" t="n"/>
     </row>
@@ -1646,14 +1646,14 @@
         </is>
       </c>
       <c r="C13" s="29" t="n">
-        <v>118921672</v>
+        <v>118401744</v>
       </c>
       <c r="D13" s="30" t="n"/>
       <c r="E13" s="30" t="n">
-        <v>-1.669</v>
+        <v>-1.742</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>11.029</v>
+        <v>11.517</v>
       </c>
     </row>
     <row r="15">
